--- a/VerveStacks_TJK_grids/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_TJK_grids/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_TJK_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{57633CC9-3ECE-4ECD-9683-D4BACB674D49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3BBBCED8-E84D-43B9-B66E-57711961F829}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -745,13 +745,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S01aH03,S05aH03,S03aH05,S05aH05,S06aH04,S02aH03,S07aH03,S02aH04,S02aH05,S07aH05,S04aH04,S01aH04,S03aH04,S05aH04,S06aH03,S04aH05,S04aH03,S07aH04,S01aH05,S06aH05,S03aH03</t>
+    <t>S02aH03,S07aH03,S07aH05,S04aH05,S03aH05,S05aH05,S06aH04,S05aH04,S06aH03,S03aH04,S02aH04,S02aH05,S04aH03,S07aH04,S01aH05,S06aH05,S01aH04,S01aH03,S05aH03,S04aH04,S03aH03</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S03aH02,S01aH01,S04aH01,S04aH06,S06aH02,S02aH06,S04aH02,S06aH01,S03aH06,S05aH01,S07aH02,S07aH06,S01aH06,S07aH01,S02aH01,S05aH02,S05aH06,S03aH01,S01aH02,S02aH02,S06aH06</t>
+    <t>S01aH01,S04aH01,S04aH06,S06aH02,S03aH01,S04aH02,S01aH06,S07aH01,S05aH01,S07aH02,S07aH06,S02aH06,S02aH01,S05aH02,S05aH06,S01aH02,S03aH06,S02aH02,S06aH06,S03aH02,S06aH01</t>
   </si>
   <si>
     <t>com_pkflx</t>
@@ -829,10 +829,10 @@
     <t>WaP</t>
   </si>
   <si>
-    <t>WaD,SaD,WaP,RaD,FaP,SaP,RaP,FaD</t>
+    <t>RaD,FaP,SaP,RaP,SaD,WaD,FaD,WaP</t>
   </si>
   <si>
-    <t>FaP,SaP,FaN,WaP,RaN,SaN,WaN,RaP</t>
+    <t>FaP,SaP,SaN,WaN,RaP,FaN,RaN,WaP</t>
   </si>
 </sst>
 </file>
@@ -24474,7 +24474,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D332EA5-4143-42E4-8698-2C642E84F3DF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85592A7B-F7D9-4ED3-9234-8B0D526CE067}">
   <dimension ref="A9:G14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -24558,7 +24558,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2381DA6B-2168-47CF-8F0D-ABD4D6ECE7B6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEE84268-F3C6-40D3-A683-3CCD2AE714FD}">
   <dimension ref="A9:AN430"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -39509,7 +39509,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B07AEF9C-7B70-490D-AF82-554BE442C636}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9741F434-65DD-4536-AAE2-366EA25BD80F}">
   <dimension ref="A9:AN36"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -39738,7 +39738,7 @@
         <v>240</v>
       </c>
       <c r="AM11">
-        <v>0.39169166666666672</v>
+        <v>0.3916916666666666</v>
       </c>
       <c r="AN11" t="s">
         <v>239</v>
@@ -39797,7 +39797,7 @@
         <v>240</v>
       </c>
       <c r="AM12">
-        <v>0.38507500000000006</v>
+        <v>0.385075</v>
       </c>
       <c r="AN12" t="s">
         <v>239</v>
@@ -39847,7 +39847,7 @@
         <v>240</v>
       </c>
       <c r="AM13">
-        <v>0.39305833333333329</v>
+        <v>0.39305833333333334</v>
       </c>
       <c r="AN13" t="s">
         <v>239</v>
@@ -39947,7 +39947,7 @@
         <v>240</v>
       </c>
       <c r="AM15">
-        <v>0.39128333333333337</v>
+        <v>0.39128333333333326</v>
       </c>
       <c r="AN15" t="s">
         <v>239</v>
@@ -39999,7 +39999,7 @@
         <v>240</v>
       </c>
       <c r="AM17">
-        <v>0.38869166666666671</v>
+        <v>0.38869166666666666</v>
       </c>
       <c r="AN17" t="s">
         <v>239</v>
@@ -40091,7 +40091,7 @@
         <v>240</v>
       </c>
       <c r="AM21">
-        <v>0.44677499999999992</v>
+        <v>0.44677499999999998</v>
       </c>
       <c r="AN21" t="s">
         <v>239</v>
@@ -40133,7 +40133,7 @@
         <v>240</v>
       </c>
       <c r="AM24">
-        <v>0.383075</v>
+        <v>0.38307500000000005</v>
       </c>
       <c r="AN24" t="s">
         <v>239</v>
@@ -40175,7 +40175,7 @@
         <v>240</v>
       </c>
       <c r="AM27">
-        <v>0.32940000000000008</v>
+        <v>0.32940000000000003</v>
       </c>
       <c r="AN27" t="s">
         <v>239</v>
@@ -40189,7 +40189,7 @@
         <v>240</v>
       </c>
       <c r="AM28">
-        <v>0.43420833333333336</v>
+        <v>0.43420833333333331</v>
       </c>
       <c r="AN28" t="s">
         <v>239</v>
@@ -40217,7 +40217,7 @@
         <v>240</v>
       </c>
       <c r="AM30">
-        <v>0.38375833333333326</v>
+        <v>0.38375833333333337</v>
       </c>
       <c r="AN30" t="s">
         <v>239</v>
@@ -40245,7 +40245,7 @@
         <v>240</v>
       </c>
       <c r="AM32">
-        <v>0.37750833333333339</v>
+        <v>0.37750833333333333</v>
       </c>
       <c r="AN32" t="s">
         <v>239</v>
@@ -40259,7 +40259,7 @@
         <v>240</v>
       </c>
       <c r="AM33">
-        <v>0.3807666666666667</v>
+        <v>0.38076666666666664</v>
       </c>
       <c r="AN33" t="s">
         <v>239</v>
@@ -40273,7 +40273,7 @@
         <v>240</v>
       </c>
       <c r="AM34">
-        <v>0.38595833333333324</v>
+        <v>0.38595833333333335</v>
       </c>
       <c r="AN34" t="s">
         <v>239</v>
@@ -40287,7 +40287,7 @@
         <v>240</v>
       </c>
       <c r="AM35">
-        <v>0.38224166666666676</v>
+        <v>0.38224166666666665</v>
       </c>
       <c r="AN35" t="s">
         <v>239</v>
@@ -40313,7 +40313,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{034AF0B5-0EE3-4F62-82BA-06C1A86BEF42}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E80177D-47F3-4275-96DF-524CF4290CF5}">
   <dimension ref="A9:AN130"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -42201,7 +42201,7 @@
         <v>243</v>
       </c>
       <c r="AM35">
-        <v>0.41446666666666659</v>
+        <v>0.41446666666666671</v>
       </c>
       <c r="AN35" t="s">
         <v>239</v>
@@ -42601,7 +42601,7 @@
         <v>243</v>
       </c>
       <c r="AM43">
-        <v>0.36053333333333337</v>
+        <v>0.36053333333333332</v>
       </c>
       <c r="AN43" t="s">
         <v>239</v>
@@ -43601,7 +43601,7 @@
         <v>243</v>
       </c>
       <c r="AM63">
-        <v>0.43653333333333338</v>
+        <v>0.43653333333333327</v>
       </c>
       <c r="AN63" t="s">
         <v>239</v>
@@ -44341,7 +44341,7 @@
         <v>246</v>
       </c>
       <c r="AM85">
-        <v>0.32833333333333337</v>
+        <v>0.32833333333333331</v>
       </c>
       <c r="AN85" t="s">
         <v>239</v>
@@ -44393,7 +44393,7 @@
         <v>243</v>
       </c>
       <c r="AM87">
-        <v>0.43253333333333327</v>
+        <v>0.43253333333333338</v>
       </c>
       <c r="AN87" t="s">
         <v>239</v>
@@ -44549,7 +44549,7 @@
         <v>246</v>
       </c>
       <c r="AM93">
-        <v>0.35586666666666661</v>
+        <v>0.35586666666666672</v>
       </c>
       <c r="AN93" t="s">
         <v>239</v>
@@ -44705,7 +44705,7 @@
         <v>243</v>
       </c>
       <c r="AM99">
-        <v>0.40779999999999994</v>
+        <v>0.4078</v>
       </c>
       <c r="AN99" t="s">
         <v>239</v>

--- a/VerveStacks_TJK_grids/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_TJK_grids/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_TJK_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3BBBCED8-E84D-43B9-B66E-57711961F829}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3477FACC-9852-48F0-9D88-41CBFDBF90BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -745,13 +745,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S02aH03,S07aH03,S07aH05,S04aH05,S03aH05,S05aH05,S06aH04,S05aH04,S06aH03,S03aH04,S02aH04,S02aH05,S04aH03,S07aH04,S01aH05,S06aH05,S01aH04,S01aH03,S05aH03,S04aH04,S03aH03</t>
+    <t>S01aH04,S01aH05,S06aH05,S01aH03,S05aH03,S03aH04,S07aH05,S03aH05,S05aH05,S06aH04,S04aH05,S02aH04,S02aH05,S05aH04,S06aH03,S04aH03,S07aH04,S04aH04,S03aH03,S02aH03,S07aH03</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S01aH01,S04aH01,S04aH06,S06aH02,S03aH01,S04aH02,S01aH06,S07aH01,S05aH01,S07aH02,S07aH06,S02aH06,S02aH01,S05aH02,S05aH06,S01aH02,S03aH06,S02aH02,S06aH06,S03aH02,S06aH01</t>
+    <t>S01aH02,S06aH01,S05aH01,S07aH02,S07aH06,S03aH02,S04aH02,S02aH06,S01aH06,S07aH01,S02aH01,S05aH02,S05aH06,S03aH06,S02aH02,S06aH06,S03aH01,S01aH01,S04aH01,S04aH06,S06aH02</t>
   </si>
   <si>
     <t>com_pkflx</t>
@@ -829,10 +829,10 @@
     <t>WaP</t>
   </si>
   <si>
-    <t>RaD,FaP,SaP,RaP,SaD,WaD,FaD,WaP</t>
+    <t>FaP,SaP,RaP,RaD,SaD,WaD,WaP,FaD</t>
   </si>
   <si>
-    <t>FaP,SaP,SaN,WaN,RaP,FaN,RaN,WaP</t>
+    <t>SaN,WaN,FaP,SaP,RaN,RaP,FaN,WaP</t>
   </si>
 </sst>
 </file>
@@ -24474,7 +24474,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85592A7B-F7D9-4ED3-9234-8B0D526CE067}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FDEC2AA-CFCF-4E20-AE2B-073CA5E853E9}">
   <dimension ref="A9:G14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -24558,7 +24558,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEE84268-F3C6-40D3-A683-3CCD2AE714FD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CAFF0AF-44AB-41C8-B08E-42D7305435D8}">
   <dimension ref="A9:AN430"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -39509,7 +39509,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9741F434-65DD-4536-AAE2-366EA25BD80F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D05D1C0F-C4D1-4293-9DAE-D986F378CCB2}">
   <dimension ref="A9:AN36"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -39738,7 +39738,7 @@
         <v>240</v>
       </c>
       <c r="AM11">
-        <v>0.3916916666666666</v>
+        <v>0.39169166666666672</v>
       </c>
       <c r="AN11" t="s">
         <v>239</v>
@@ -39973,7 +39973,7 @@
         <v>240</v>
       </c>
       <c r="AM16">
-        <v>0.39234166666666659</v>
+        <v>0.39234166666666664</v>
       </c>
       <c r="AN16" t="s">
         <v>239</v>
@@ -40025,7 +40025,7 @@
         <v>240</v>
       </c>
       <c r="AM18">
-        <v>0.32980833333333331</v>
+        <v>0.32980833333333337</v>
       </c>
       <c r="AN18" t="s">
         <v>239</v>
@@ -40051,7 +40051,7 @@
         <v>240</v>
       </c>
       <c r="AM19">
-        <v>0.32800833333333329</v>
+        <v>0.3280083333333334</v>
       </c>
       <c r="AN19" t="s">
         <v>239</v>
@@ -40119,7 +40119,7 @@
         <v>240</v>
       </c>
       <c r="AM23">
-        <v>0.38974999999999999</v>
+        <v>0.38975000000000004</v>
       </c>
       <c r="AN23" t="s">
         <v>239</v>
@@ -40133,7 +40133,7 @@
         <v>240</v>
       </c>
       <c r="AM24">
-        <v>0.38307500000000005</v>
+        <v>0.383075</v>
       </c>
       <c r="AN24" t="s">
         <v>239</v>
@@ -40175,7 +40175,7 @@
         <v>240</v>
       </c>
       <c r="AM27">
-        <v>0.32940000000000003</v>
+        <v>0.32939999999999997</v>
       </c>
       <c r="AN27" t="s">
         <v>239</v>
@@ -40203,7 +40203,7 @@
         <v>240</v>
       </c>
       <c r="AM29">
-        <v>0.3937666666666666</v>
+        <v>0.39376666666666665</v>
       </c>
       <c r="AN29" t="s">
         <v>239</v>
@@ -40245,7 +40245,7 @@
         <v>240</v>
       </c>
       <c r="AM32">
-        <v>0.37750833333333333</v>
+        <v>0.37750833333333339</v>
       </c>
       <c r="AN32" t="s">
         <v>239</v>
@@ -40259,7 +40259,7 @@
         <v>240</v>
       </c>
       <c r="AM33">
-        <v>0.38076666666666664</v>
+        <v>0.3807666666666667</v>
       </c>
       <c r="AN33" t="s">
         <v>239</v>
@@ -40273,7 +40273,7 @@
         <v>240</v>
       </c>
       <c r="AM34">
-        <v>0.38595833333333335</v>
+        <v>0.3859583333333334</v>
       </c>
       <c r="AN34" t="s">
         <v>239</v>
@@ -40301,7 +40301,7 @@
         <v>240</v>
       </c>
       <c r="AM36">
-        <v>0.4412666666666667</v>
+        <v>0.44126666666666664</v>
       </c>
       <c r="AN36" t="s">
         <v>239</v>
@@ -40313,7 +40313,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E80177D-47F3-4275-96DF-524CF4290CF5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F77A67E0-8F61-4903-8D9C-2A58DF982442}">
   <dimension ref="A9:AN130"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -40963,7 +40963,7 @@
         <v>245</v>
       </c>
       <c r="AM16">
-        <v>0.36149999999999999</v>
+        <v>0.36149999999999993</v>
       </c>
       <c r="AN16" t="s">
         <v>239</v>
@@ -41283,7 +41283,7 @@
         <v>245</v>
       </c>
       <c r="AM20">
-        <v>0.36726666666666669</v>
+        <v>0.36726666666666663</v>
       </c>
       <c r="AN20" t="s">
         <v>239</v>

--- a/VerveStacks_TJK_grids/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_TJK_grids/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_TJK_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3477FACC-9852-48F0-9D88-41CBFDBF90BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F0C5FE1A-8D32-4D34-8F06-C63560D1387F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -745,13 +745,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S01aH04,S01aH05,S06aH05,S01aH03,S05aH03,S03aH04,S07aH05,S03aH05,S05aH05,S06aH04,S04aH05,S02aH04,S02aH05,S05aH04,S06aH03,S04aH03,S07aH04,S04aH04,S03aH03,S02aH03,S07aH03</t>
+    <t>S04aH03,S07aH04,S02aH04,S02aH05,S04aH05,S07aH05,S03aH03,S01aH05,S06aH05,S05aH04,S06aH03,S01aH04,S04aH04,S02aH03,S07aH03,S03aH04,S03aH05,S05aH05,S06aH04,S01aH03,S05aH03</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S01aH02,S06aH01,S05aH01,S07aH02,S07aH06,S03aH02,S04aH02,S02aH06,S01aH06,S07aH01,S02aH01,S05aH02,S05aH06,S03aH06,S02aH02,S06aH06,S03aH01,S01aH01,S04aH01,S04aH06,S06aH02</t>
+    <t>S02aH01,S05aH02,S05aH06,S02aH06,S04aH02,S02aH02,S06aH06,S01aH02,S01aH06,S07aH01,S03aH02,S03aH06,S01aH01,S04aH01,S04aH06,S06aH02,S05aH01,S07aH02,S07aH06,S03aH01,S06aH01</t>
   </si>
   <si>
     <t>com_pkflx</t>
@@ -829,10 +829,10 @@
     <t>WaP</t>
   </si>
   <si>
-    <t>FaP,SaP,RaP,RaD,SaD,WaD,WaP,FaD</t>
+    <t>SaD,RaD,FaP,SaP,WaP,FaD,RaP,WaD</t>
   </si>
   <si>
-    <t>SaN,WaN,FaP,SaP,RaN,RaP,FaN,WaP</t>
+    <t>FaP,SaP,FaN,WaP,RaN,RaP,SaN,WaN</t>
   </si>
 </sst>
 </file>
@@ -24474,7 +24474,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FDEC2AA-CFCF-4E20-AE2B-073CA5E853E9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27AE77D2-0CA0-46E0-95C9-B4E98874C847}">
   <dimension ref="A9:G14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -24558,7 +24558,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CAFF0AF-44AB-41C8-B08E-42D7305435D8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B911C2F4-653A-4751-97BE-8204F21A3BCD}">
   <dimension ref="A9:AN430"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -39509,7 +39509,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D05D1C0F-C4D1-4293-9DAE-D986F378CCB2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65CCA8AB-25FD-4617-987A-87209578B0C0}">
   <dimension ref="A9:AN36"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -39947,7 +39947,7 @@
         <v>240</v>
       </c>
       <c r="AM15">
-        <v>0.39128333333333326</v>
+        <v>0.39128333333333337</v>
       </c>
       <c r="AN15" t="s">
         <v>239</v>
@@ -40025,7 +40025,7 @@
         <v>240</v>
       </c>
       <c r="AM18">
-        <v>0.32980833333333337</v>
+        <v>0.32980833333333331</v>
       </c>
       <c r="AN18" t="s">
         <v>239</v>
@@ -40051,7 +40051,7 @@
         <v>240</v>
       </c>
       <c r="AM19">
-        <v>0.3280083333333334</v>
+        <v>0.32800833333333329</v>
       </c>
       <c r="AN19" t="s">
         <v>239</v>
@@ -40119,7 +40119,7 @@
         <v>240</v>
       </c>
       <c r="AM23">
-        <v>0.38975000000000004</v>
+        <v>0.38974999999999999</v>
       </c>
       <c r="AN23" t="s">
         <v>239</v>
@@ -40231,7 +40231,7 @@
         <v>240</v>
       </c>
       <c r="AM31">
-        <v>0.4003666666666667</v>
+        <v>0.40036666666666659</v>
       </c>
       <c r="AN31" t="s">
         <v>239</v>
@@ -40245,7 +40245,7 @@
         <v>240</v>
       </c>
       <c r="AM32">
-        <v>0.37750833333333339</v>
+        <v>0.37750833333333333</v>
       </c>
       <c r="AN32" t="s">
         <v>239</v>
@@ -40273,7 +40273,7 @@
         <v>240</v>
       </c>
       <c r="AM34">
-        <v>0.3859583333333334</v>
+        <v>0.38595833333333335</v>
       </c>
       <c r="AN34" t="s">
         <v>239</v>
@@ -40313,7 +40313,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F77A67E0-8F61-4903-8D9C-2A58DF982442}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49D80646-323C-49C3-9BEF-FEBD2F6EAA3E}">
   <dimension ref="A9:AN130"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -40803,7 +40803,7 @@
         <v>248</v>
       </c>
       <c r="AM14">
-        <v>0.45596666666666663</v>
+        <v>0.45596666666666669</v>
       </c>
       <c r="AN14" t="s">
         <v>239</v>
@@ -41443,7 +41443,7 @@
         <v>248</v>
       </c>
       <c r="AM22">
-        <v>0.42900000000000005</v>
+        <v>0.42899999999999999</v>
       </c>
       <c r="AN22" t="s">
         <v>239</v>
@@ -42201,7 +42201,7 @@
         <v>243</v>
       </c>
       <c r="AM35">
-        <v>0.41446666666666671</v>
+        <v>0.41446666666666659</v>
       </c>
       <c r="AN35" t="s">
         <v>239</v>
@@ -42351,7 +42351,7 @@
         <v>248</v>
       </c>
       <c r="AM38">
-        <v>0.43793333333333329</v>
+        <v>0.43793333333333334</v>
       </c>
       <c r="AN38" t="s">
         <v>239</v>
@@ -42551,7 +42551,7 @@
         <v>248</v>
       </c>
       <c r="AM42">
-        <v>0.36443333333333333</v>
+        <v>0.36443333333333339</v>
       </c>
       <c r="AN42" t="s">
         <v>239</v>
@@ -42601,7 +42601,7 @@
         <v>243</v>
       </c>
       <c r="AM43">
-        <v>0.36053333333333332</v>
+        <v>0.36053333333333337</v>
       </c>
       <c r="AN43" t="s">
         <v>239</v>
@@ -42951,7 +42951,7 @@
         <v>248</v>
       </c>
       <c r="AM50">
-        <v>0.51400000000000001</v>
+        <v>0.5139999999999999</v>
       </c>
       <c r="AN50" t="s">
         <v>239</v>
@@ -43601,7 +43601,7 @@
         <v>243</v>
       </c>
       <c r="AM63">
-        <v>0.43653333333333327</v>
+        <v>0.43653333333333338</v>
       </c>
       <c r="AN63" t="s">
         <v>239</v>
@@ -43751,7 +43751,7 @@
         <v>248</v>
       </c>
       <c r="AM66">
-        <v>0.43113333333333331</v>
+        <v>0.43113333333333337</v>
       </c>
       <c r="AN66" t="s">
         <v>239</v>
@@ -43951,7 +43951,7 @@
         <v>248</v>
       </c>
       <c r="AM70">
-        <v>0.36463333333333331</v>
+        <v>0.36463333333333336</v>
       </c>
       <c r="AN70" t="s">
         <v>239</v>
@@ -44159,7 +44159,7 @@
         <v>248</v>
       </c>
       <c r="AM78">
-        <v>0.37136666666666662</v>
+        <v>0.37136666666666668</v>
       </c>
       <c r="AN78" t="s">
         <v>239</v>
@@ -44341,7 +44341,7 @@
         <v>246</v>
       </c>
       <c r="AM85">
-        <v>0.32833333333333331</v>
+        <v>0.32833333333333337</v>
       </c>
       <c r="AN85" t="s">
         <v>239</v>
@@ -44393,7 +44393,7 @@
         <v>243</v>
       </c>
       <c r="AM87">
-        <v>0.43253333333333338</v>
+        <v>0.43253333333333327</v>
       </c>
       <c r="AN87" t="s">
         <v>239</v>
@@ -44549,7 +44549,7 @@
         <v>246</v>
       </c>
       <c r="AM93">
-        <v>0.35586666666666672</v>
+        <v>0.35586666666666661</v>
       </c>
       <c r="AN93" t="s">
         <v>239</v>
@@ -44575,7 +44575,7 @@
         <v>248</v>
       </c>
       <c r="AM94">
-        <v>0.41776666666666662</v>
+        <v>0.41776666666666668</v>
       </c>
       <c r="AN94" t="s">
         <v>239</v>
@@ -44705,7 +44705,7 @@
         <v>243</v>
       </c>
       <c r="AM99">
-        <v>0.4078</v>
+        <v>0.40779999999999994</v>
       </c>
       <c r="AN99" t="s">
         <v>239</v>
@@ -44783,7 +44783,7 @@
         <v>248</v>
       </c>
       <c r="AM102">
-        <v>0.44166666666666665</v>
+        <v>0.44166666666666671</v>
       </c>
       <c r="AN102" t="s">
         <v>239</v>

--- a/VerveStacks_TJK_grids/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_TJK_grids/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_TJK_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F0C5FE1A-8D32-4D34-8F06-C63560D1387F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{713B9D84-7015-4B6E-8EB2-3DD560954D4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -745,13 +745,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S04aH03,S07aH04,S02aH04,S02aH05,S04aH05,S07aH05,S03aH03,S01aH05,S06aH05,S05aH04,S06aH03,S01aH04,S04aH04,S02aH03,S07aH03,S03aH04,S03aH05,S05aH05,S06aH04,S01aH03,S05aH03</t>
+    <t>S04aH03,S07aH04,S02aH04,S02aH05,S03aH05,S05aH05,S06aH04,S03aH03,S04aH04,S01aH04,S01aH03,S05aH03,S04aH05,S01aH05,S06aH05,S02aH03,S07aH03,S05aH04,S06aH03,S03aH04,S07aH05</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S02aH01,S05aH02,S05aH06,S02aH06,S04aH02,S02aH02,S06aH06,S01aH02,S01aH06,S07aH01,S03aH02,S03aH06,S01aH01,S04aH01,S04aH06,S06aH02,S05aH01,S07aH02,S07aH06,S03aH01,S06aH01</t>
+    <t>S02aH01,S05aH02,S05aH06,S02aH06,S03aH01,S02aH02,S06aH06,S03aH06,S03aH02,S01aH02,S01aH01,S04aH01,S04aH06,S06aH02,S06aH01,S01aH06,S07aH01,S05aH01,S07aH02,S07aH06,S04aH02</t>
   </si>
   <si>
     <t>com_pkflx</t>
@@ -829,10 +829,10 @@
     <t>WaP</t>
   </si>
   <si>
-    <t>SaD,RaD,FaP,SaP,WaP,FaD,RaP,WaD</t>
+    <t>FaD,RaP,FaP,SaP,WaP,SaD,WaD,RaD</t>
   </si>
   <si>
-    <t>FaP,SaP,FaN,WaP,RaN,RaP,SaN,WaN</t>
+    <t>SaN,WaN,WaP,RaP,FaN,RaN,FaP,SaP</t>
   </si>
 </sst>
 </file>
@@ -24474,7 +24474,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27AE77D2-0CA0-46E0-95C9-B4E98874C847}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1DCAEEA-81E3-4566-9944-CE243067D95B}">
   <dimension ref="A9:G14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -24558,7 +24558,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B911C2F4-653A-4751-97BE-8204F21A3BCD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{563317F3-3646-4044-982B-11817D1738BB}">
   <dimension ref="A9:AN430"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -39509,7 +39509,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65CCA8AB-25FD-4617-987A-87209578B0C0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEDF06EA-8F65-4473-9337-C9AF1FCB8754}">
   <dimension ref="A9:AN36"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -39847,7 +39847,7 @@
         <v>240</v>
       </c>
       <c r="AM13">
-        <v>0.39305833333333334</v>
+        <v>0.39305833333333329</v>
       </c>
       <c r="AN13" t="s">
         <v>239</v>
@@ -40119,7 +40119,7 @@
         <v>240</v>
       </c>
       <c r="AM23">
-        <v>0.38974999999999999</v>
+        <v>0.38975000000000004</v>
       </c>
       <c r="AN23" t="s">
         <v>239</v>
@@ -40175,7 +40175,7 @@
         <v>240</v>
       </c>
       <c r="AM27">
-        <v>0.32939999999999997</v>
+        <v>0.32940000000000003</v>
       </c>
       <c r="AN27" t="s">
         <v>239</v>
@@ -40203,7 +40203,7 @@
         <v>240</v>
       </c>
       <c r="AM29">
-        <v>0.39376666666666665</v>
+        <v>0.3937666666666666</v>
       </c>
       <c r="AN29" t="s">
         <v>239</v>
@@ -40313,7 +40313,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49D80646-323C-49C3-9BEF-FEBD2F6EAA3E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DA64C0F-9545-4BFE-ABD9-4DE6930D0FCC}">
   <dimension ref="A9:AN130"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -40803,7 +40803,7 @@
         <v>248</v>
       </c>
       <c r="AM14">
-        <v>0.45596666666666669</v>
+        <v>0.45596666666666663</v>
       </c>
       <c r="AN14" t="s">
         <v>239</v>
@@ -41443,7 +41443,7 @@
         <v>248</v>
       </c>
       <c r="AM22">
-        <v>0.42899999999999999</v>
+        <v>0.42900000000000005</v>
       </c>
       <c r="AN22" t="s">
         <v>239</v>
@@ -42201,7 +42201,7 @@
         <v>243</v>
       </c>
       <c r="AM35">
-        <v>0.41446666666666659</v>
+        <v>0.41446666666666671</v>
       </c>
       <c r="AN35" t="s">
         <v>239</v>
@@ -42351,7 +42351,7 @@
         <v>248</v>
       </c>
       <c r="AM38">
-        <v>0.43793333333333334</v>
+        <v>0.43793333333333329</v>
       </c>
       <c r="AN38" t="s">
         <v>239</v>
@@ -42551,7 +42551,7 @@
         <v>248</v>
       </c>
       <c r="AM42">
-        <v>0.36443333333333339</v>
+        <v>0.36443333333333333</v>
       </c>
       <c r="AN42" t="s">
         <v>239</v>
@@ -42601,7 +42601,7 @@
         <v>243</v>
       </c>
       <c r="AM43">
-        <v>0.36053333333333337</v>
+        <v>0.36053333333333332</v>
       </c>
       <c r="AN43" t="s">
         <v>239</v>
@@ -42951,7 +42951,7 @@
         <v>248</v>
       </c>
       <c r="AM50">
-        <v>0.5139999999999999</v>
+        <v>0.51400000000000001</v>
       </c>
       <c r="AN50" t="s">
         <v>239</v>
@@ -43601,7 +43601,7 @@
         <v>243</v>
       </c>
       <c r="AM63">
-        <v>0.43653333333333338</v>
+        <v>0.43653333333333327</v>
       </c>
       <c r="AN63" t="s">
         <v>239</v>
@@ -43751,7 +43751,7 @@
         <v>248</v>
       </c>
       <c r="AM66">
-        <v>0.43113333333333337</v>
+        <v>0.43113333333333331</v>
       </c>
       <c r="AN66" t="s">
         <v>239</v>
@@ -43951,7 +43951,7 @@
         <v>248</v>
       </c>
       <c r="AM70">
-        <v>0.36463333333333336</v>
+        <v>0.36463333333333331</v>
       </c>
       <c r="AN70" t="s">
         <v>239</v>
@@ -44159,7 +44159,7 @@
         <v>248</v>
       </c>
       <c r="AM78">
-        <v>0.37136666666666668</v>
+        <v>0.37136666666666662</v>
       </c>
       <c r="AN78" t="s">
         <v>239</v>
@@ -44393,7 +44393,7 @@
         <v>243</v>
       </c>
       <c r="AM87">
-        <v>0.43253333333333327</v>
+        <v>0.43253333333333338</v>
       </c>
       <c r="AN87" t="s">
         <v>239</v>
@@ -44549,7 +44549,7 @@
         <v>246</v>
       </c>
       <c r="AM93">
-        <v>0.35586666666666661</v>
+        <v>0.35586666666666672</v>
       </c>
       <c r="AN93" t="s">
         <v>239</v>
@@ -44575,7 +44575,7 @@
         <v>248</v>
       </c>
       <c r="AM94">
-        <v>0.41776666666666668</v>
+        <v>0.41776666666666662</v>
       </c>
       <c r="AN94" t="s">
         <v>239</v>
@@ -44705,7 +44705,7 @@
         <v>243</v>
       </c>
       <c r="AM99">
-        <v>0.40779999999999994</v>
+        <v>0.4078</v>
       </c>
       <c r="AN99" t="s">
         <v>239</v>
@@ -44783,7 +44783,7 @@
         <v>248</v>
       </c>
       <c r="AM102">
-        <v>0.44166666666666671</v>
+        <v>0.44166666666666665</v>
       </c>
       <c r="AN102" t="s">
         <v>239</v>
